--- a/documentation/data_dictionary.xlsx
+++ b/documentation/data_dictionary.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="raw_data_dictionary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="excluded_columns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="phase2_tables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="phase2_columns" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1802,4 +1804,5376 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>row_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_class_breakdown</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PUBLIC/DERIVED</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>136</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{'PUBLIC': 69, 'DERIVED': 62, 'SIMULATED': 5}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Origins from manufacturing_site; destinations one DC per destination_country; warehouse locations simulated. Coordinates left NULL (never fabricated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>131</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 131}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Preserves each raw location string and how it mapped to a location_id (match_method).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 4}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>One illustrative HS-prefixed code per product category. NOT official US HTS (code_type).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 20}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5 SKUs per renewable-energy category; unit_weight/value seeded from the observed per-unit source distribution (median of weight/qty, value/qty).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DERIVED/SIMULATED</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>128</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 73, 'SIMULATED': 55}</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Unified registry: suppliers (real vendors), carriers, brokers, customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>73</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 73}</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>One per real source vendor; location = most-used manufacturing site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 5}</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5 regional DCs (config); location FK to dim_location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 12}</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12 fictional carriers across all modes (config).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>785</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 785}</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Distinct (origin, destination, mode) combinations; standard_transit_days = mode/region standard (source has no departure timestamp). estimated_distance NULL (not measurable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2311</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 2311}</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>One rate per (pool carrier, lane); rate_per_kg ~ observed mode freight/kg with deterministic carrier spread; single wide effective window (no overlap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6233</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 6233}</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Groups shipment lines sharing a source PO reference; else one derived PO per line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10324</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 10324}</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>One per staged shipment (source_record_id lineage). Real value/qty/delivery preserved; ship dates derived from mode/lane transit (ship_date_derived_flag=1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>87046</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 87046}</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mode-aware milestone templates; timestamps reconcile to shipment dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 10012}</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>One per delivered shipment; charges from the applicable rate card (+small rating noise within audit tolerance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>21389</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 21389}</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BASE_FREIGHT / FUEL_SURCHARGE / ACCESSORIAL / TAX lines; sum to total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1432</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 1432}</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Low-frequency, mode-plausible charges; clean baseline all contractually allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 10012}</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>One per delivered shipment; generic role-based recipient (no PII).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>291</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 291}</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Risk-weighted legitimate claims (late/high-value/ocean more likely).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 7200}</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Monthly per carrier x lane; utilization &lt;=100% with seasonal variation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>39989</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>{'SIMULATED': 39989}</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4-stage workflow; chronological; paid =&gt; approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10324</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{'DERIVED': 10324}</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Per shipment by accounting period; expected freight vs received invoice; RELEASED only when invoice received &amp; approved.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D234"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>null_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>location_name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>state_or_province</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>location_type</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>xref_id</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>raw_location_string</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>raw_field</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>match_method</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>hts_code</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>product_category</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>effective_end_date</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>hazardous_material_flag</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>customs_document_required_flag</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>code_type</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>product_sku</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>product_category</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>product_description</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>unit_of_measure</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>unit_weight_kg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>unit_value_usd</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hts_code</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>hazardous_material_flag</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>temperature_controlled_flag</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stackable_flag</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>partner_name</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>partner_type</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>24.22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>supplier_id</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>supplier_name</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>supplier_location_id</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>primary_product_category</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>26.03</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>warehouse_id</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>warehouse_name</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>warehouse_type</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>capacity_weight_kg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>capacity_pallets</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>carrier_id</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>carrier_name</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>carrier_type</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>primary_mode</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>operating_region</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>payment_terms</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>default_currency</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>effective_end_date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>lane_id</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>origin_location_id</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>destination_location_id</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>origin_name</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>destination_name</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>lane_region</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>standard_transit_days</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>estimated_distance</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>distance_unit</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>transit_derivation_method</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>active_flag</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>rate_id</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>carrier_id</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>lane_id</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>effective_end_date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>rate_basis</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>base_rate</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>rate_per_kg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>rate_per_shipment</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>minimum_charge</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>fuel_percentage</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>detention_allowed_flag</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>demurrage_allowed_flag</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>storage_allowed_flag</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>po_id</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>po_number</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>supplier_id</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ordered_quantity</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>purchase_value</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>po_created_date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>expected_ship_date</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>expected_delivery_date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>po_status</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>source_record_id</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>po_id</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>carrier_id</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>lane_id</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>origin_location_id</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>destination_location_id</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>warehouse_id</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>47.66</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>shipment_mode</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>incoterm</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>52.34</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>booking_date</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>planned_ship_date</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>actual_ship_date</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>planned_delivery_date</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>actual_delivery_date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>planned_quantity</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>shipped_quantity</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>delivered_quantity</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>shipment_weight_kg</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>shipment_value_usd</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>shipment_status</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>customs_required_flag</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>hazmat_flag</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>is_delivered_flag</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ship_date_derived_flag</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>weight_imputed_flag</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>mode_imputed_flag</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>milestone_id</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>milestone_type</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>milestone_sequence</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>planned_timestamp</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>actual_timestamp</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>milestone_status</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>exception_reason</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>carrier_id</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>invoice_date</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>service_period_start</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>service_period_end</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>base_charge</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>fuel_surcharge</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>accessorial_charge</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>tax_amount</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>invoice_total</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>payment_status</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>invoice_line_id</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>line_type</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>accessorial_id</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>charge_type</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>charge_amount</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>supporting_document_flag</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>contractually_allowed_flag</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>pod_id</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>delivery_timestamp</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>received_timestamp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>recipient_name</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>pod_status</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>claim_id</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>claim_type</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>claim_amount</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>claim_status</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>root_cause</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>created_date</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>closed_date</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>capacity_id</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>carrier_id</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>lane_id</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>period_start</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>period_month</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>available_capacity_kg</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>booked_capacity_kg</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>utilized_capacity_kg</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>capacity_utilization_pct</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>approval_id</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>invoice_id</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>approval_stage</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>assigned_role</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>submitted_timestamp</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>approved_timestamp</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>rejection_reason</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>accrual_id</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>accounting_period</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>expected_freight_cost</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>invoice_received_flag</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>actual_invoice_cost</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>accrual_status</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>accrual_created_date</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>accrual_release_date</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>accrual_variance</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>data_class</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>